--- a/financial_advisor_forms/033_investment_strategy_assessment--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/033_investment_strategy_assessment--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk Tolerance</t>
+          <t>What is your risk tolerance level?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Investment Goals</t>
+          <t>What are your short-term and long-term investment goals?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk Level</t>
+          <t>How would you describe your current investment risk level?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Investment Type</t>
+          <t>Which investments would you like to consider?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Asset Allocation</t>
+          <t>Please choose your asset allocation strategy -</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Investment Frequency</t>
+          <t>How often do you plan to invest?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,76 +663,76 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Investment Amount</t>
+          <t>How much do you plan to invest each time?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>investment_frequency</t>
+          <t>investment_frequency_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Investment Frequency</t>
+          <t>How often do you plan to invest in the next month?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>investment_amount_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk Level</t>
+          <t>How much do you plan to invest in the next month?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>investment_type</t>
+          <t>other_invest_types</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Investment Type</t>
+          <t>Are there any other investment types you'd like to consider?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>asset_allocation</t>
+          <t>asset_allocation_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Asset Allocation</t>
+          <t>How do you plan to allocate your assets for this investment?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>risk_level_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How would you describe your risk level for this investment?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -776,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -804,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -821,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -838,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -872,68 +895,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>very_conservative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>Very Conservative</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bonds</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bonds</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>real_estate</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -945,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
@@ -962,182 +985,454 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>very_conservative</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Very Conservative</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>commodities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aggressive</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>risk_level_choices</t>
+          <t>investment_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>asset_allocation_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>conservative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>Conservative</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>asset_allocation_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bonds</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bonds</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>asset_allocation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>real_estate</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>asset_allocation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Balanced</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>investment_type_choices</t>
+          <t>investment_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>investment_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>investment_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>investment_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>investment_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>investment_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>investment_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>asset_allocation_2_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>asset_allocation_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>asset_allocation_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>asset_allocation_2_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>risk_level_2_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>very_conservative</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Very Conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>risk_level_2_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>risk_level_2_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>risk_level_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
